--- a/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
+++ b/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
@@ -1374,7 +1374,7 @@
         <is>
           <t>1号屋
 4858呎 (4+房)
-(18年-12月)
+(18年-12月-23日)
 $6.67亿
 $137,201/呎</t>
         </is>
@@ -1383,7 +1383,7 @@
         <is>
           <t>2号屋
 4479呎 (4+房)
-(18年-08月)
+(18年-08月-05日)
 $4.95亿
 $110,538/呎</t>
         </is>
@@ -1401,7 +1401,7 @@
         <is>
           <t>5号屋
 4471呎 (4+房)
-(25年-10月)
+(25年-10月-23日)
 $3.52亿
 $78,730/呎</t>
         </is>
@@ -1410,7 +1410,7 @@
         <is>
           <t>6号屋
 4391呎 (4+房)
-(15年-02月)
+(15年-02月-26日)
 $5.06亿
 $115,247/呎</t>
         </is>
@@ -1419,7 +1419,7 @@
         <is>
           <t>7号屋
 4470呎 (4+房)
-(15年-02月)
+(15年-02月-08日)
 $4.92亿
 $109,998/呎</t>
         </is>
@@ -1435,7 +1435,7 @@
         <is>
           <t>8号屋
 5221呎 (4+房)
-(18年-08月)
+(18年-08月-06日)
 $7.30亿
 $139,820/呎</t>
         </is>
@@ -1444,7 +1444,7 @@
         <is>
           <t>9号屋
 3905呎 (4+房)
-(18年-12月)
+(18年-12月-27日)
 $4.58亿
 $117,286/呎</t>
         </is>
@@ -1453,7 +1453,7 @@
         <is>
           <t>10号屋
 3845呎 (3房)
-(18年-12月)
+(18年-12月-23日)
 $4.58亿
 $119,116/呎</t>
         </is>
@@ -1462,7 +1462,7 @@
         <is>
           <t>11号屋
 3942呎 (4+房)
-(15年-02月)
+(15年-02月-12日)
 $3.92亿
 $99,461/呎</t>
         </is>
@@ -1471,7 +1471,7 @@
         <is>
           <t>12号屋
 4030呎 (3房)
-(14年-08月)
+(14年-08月-14日)
 $4.13亿
 $102,392/呎</t>
         </is>
@@ -1480,7 +1480,7 @@
         <is>
           <t>15号屋
 3885呎 (4+房)
-(18年-11月)
+(18年-11月-08日)
 $4.50亿
 $115,830/呎</t>
         </is>

--- a/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
+++ b/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +154,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -181,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,6 +238,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1048,7 +1057,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1063,11 +1072,11 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3845</v>
+        <v>3942</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1076,14 +1085,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2018-12-23</t>
+          <t>2015-02-12</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>458000000</v>
+        <v>392074000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>119116</v>
+        <v>99461</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1094,7 +1103,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>12号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,11 +1118,11 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3942</v>
+        <v>4030</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1122,14 +1131,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
+          <t>2014-08-14</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>392074000</v>
+        <v>412638000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>99461</v>
+        <v>102392</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1140,7 +1149,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>15号屋</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1155,11 +1164,11 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4030</v>
+        <v>3885</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1168,62 +1177,16 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2014-08-14</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>412638000</v>
+        <v>450000000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>102392</v>
+        <v>115830</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>15号屋</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>3885</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>115830</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1298,7 +1261,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>12 套</t>
+          <t>11 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1313,7 +1276,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>11 套</t>
+          <t>10 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1451,15 +1414,6 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>10号屋
-3845呎 (3房)
-(18年-12月-23日)
-$4.58亿
-$119,116/呎</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
           <t>11号屋
 3942呎 (4+房)
 (15年-02月-12日)
@@ -1467,7 +1421,7 @@
 $99,461/呎</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>12号屋
 4030呎 (3房)
@@ -1476,7 +1430,7 @@
 $102,392/呎</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>15号屋
 3885呎 (4+房)
@@ -1485,6 +1439,7 @@
 $115,830/呎</t>
         </is>
       </c>
+      <c r="G7" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
+++ b/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -154,12 +154,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,60 +181,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -621,6 +612,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -678,6 +673,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -713,7 +728,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2018-12-23</t>
+          <t>2018-12-24</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -724,6 +739,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>666523000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>137201</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -759,7 +790,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -770,6 +801,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>495100000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>110538</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -820,6 +867,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -855,7 +922,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -866,6 +933,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>352000000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>78730</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -901,7 +984,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2015-02-26</t>
+          <t>2015-02-27</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -912,6 +995,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>506049000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>115247</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -947,7 +1046,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2015-02-08</t>
+          <t>2015-02-09</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -958,6 +1057,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>491693000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>109998</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -993,7 +1108,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1004,6 +1119,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>730000000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>139820</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1039,7 +1170,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2018-12-27</t>
+          <t>2018-12-28</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1050,6 +1181,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>458000000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>117286</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1057,7 +1204,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1072,11 +1219,11 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3942</v>
+        <v>3845</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1085,16 +1232,32 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
+          <t>2018-12-24</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>392074000</v>
+        <v>458000000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>99461</v>
+        <v>119116</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>458000000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>119116</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1103,7 +1266,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1118,11 +1281,11 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4030</v>
+        <v>3942</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1131,16 +1294,32 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2014-08-14</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>412638000</v>
+        <v>392074000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>102392</v>
+        <v>99461</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>392074000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>99461</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1149,44 +1328,122 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>12号屋</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>4030</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2014-08-15</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>412638000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>102392</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>412638000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>102392</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>15号屋</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>3885</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>450000000</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>115830</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>115830</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1194,7 +1451,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1261,22 +1518,22 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>12 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
           <t>11 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>10 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1337,7 +1594,7 @@
         <is>
           <t>1号屋
 4858呎 (4+房)
-(18年-12月-23日)
+(18年-12月-24日)
 $6.67亿
 $137,201/呎</t>
         </is>
@@ -1346,7 +1603,7 @@
         <is>
           <t>2号屋
 4479呎 (4+房)
-(18年-08月-05日)
+(18年-08月-06日)
 $4.95亿
 $110,538/呎</t>
         </is>
@@ -1364,7 +1621,7 @@
         <is>
           <t>5号屋
 4471呎 (4+房)
-(25年-10月-23日)
+(25年-10月-24日)
 $3.52亿
 $78,730/呎</t>
         </is>
@@ -1373,7 +1630,7 @@
         <is>
           <t>6号屋
 4391呎 (4+房)
-(15年-02月-26日)
+(15年-02月-27日)
 $5.06亿
 $115,247/呎</t>
         </is>
@@ -1382,7 +1639,7 @@
         <is>
           <t>7号屋
 4470呎 (4+房)
-(15年-02月-08日)
+(15年-02月-09日)
 $4.92亿
 $109,998/呎</t>
         </is>
@@ -1398,7 +1655,7 @@
         <is>
           <t>8号屋
 5221呎 (4+房)
-(18年-08月-06日)
+(18年-08月-07日)
 $7.30亿
 $139,820/呎</t>
         </is>
@@ -1407,39 +1664,47 @@
         <is>
           <t>9号屋
 3905呎 (4+房)
-(18年-12月-27日)
+(18年-12月-28日)
 $4.58亿
 $117,286/呎</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
+          <t>10号屋
+3845呎 (3房)
+(18年-12月-24日)
+$4.58亿
+$119,116/呎</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
           <t>11号屋
 3942呎 (4+房)
-(15年-02月-12日)
+(15年-02月-13日)
 $3.92亿
 $99,461/呎</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>12号屋
 4030呎 (3房)
-(14年-08月-14日)
+(14年-08月-15日)
 $4.13亿
 $102,392/呎</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>15号屋
 3885呎 (4+房)
-(18年-11月-08日)
+(18年-11月-09日)
 $4.50亿
 $115,830/呎</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
+++ b/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +154,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -181,57 +187,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -612,10 +621,6 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -673,26 +678,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>最高折扣</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>折实总价 (港币)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>折实呎价 (港币/呎)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>付款办法</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -728,7 +713,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2018-12-24</t>
+          <t>2018-12-23</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -739,22 +724,6 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>666523000</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>137201</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -790,7 +759,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -801,22 +770,6 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>495100000</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>110538</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -867,26 +820,6 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -922,7 +855,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -933,22 +866,6 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>352000000</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>78730</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -956,7 +873,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6号屋</t>
+          <t>8号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -975,7 +892,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4391</v>
+        <v>5221</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -984,32 +901,16 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2015-02-27</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>506049000</v>
+        <v>730000000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>115247</v>
+        <v>139820</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>506049000</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>115247</v>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1018,7 +919,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>7号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1037,7 +938,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4470</v>
+        <v>3905</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1046,32 +947,16 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2015-02-09</t>
+          <t>2018-12-27</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>491693000</v>
+        <v>458000000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>109998</v>
+        <v>117286</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>491693000</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>109998</v>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1080,7 +965,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>8号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1095,11 +980,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5221</v>
+        <v>3845</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1108,32 +993,16 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-12-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>730000000</v>
+        <v>458000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>139820</v>
+        <v>119116</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>730000000</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>139820</v>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1142,7 +1011,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1161,7 +1030,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3905</v>
+        <v>3942</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1170,32 +1039,16 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2018-12-28</t>
+          <t>2015-02-12</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>458000000</v>
+        <v>392074000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>117286</v>
+        <v>99461</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>458000000</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>117286</v>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1204,7 +1057,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>12号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1223,7 +1076,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3845</v>
+        <v>4030</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1232,32 +1085,16 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2018-12-24</t>
+          <t>2014-08-14</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>458000000</v>
+        <v>412638000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>119116</v>
+        <v>102392</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>458000000</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>119116</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1266,7 +1103,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>15号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1285,7 +1122,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3942</v>
+        <v>3885</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1294,156 +1131,16 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2015-02-13</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>392074000</v>
+        <v>450000000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>99461</v>
+        <v>115830</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>392074000</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>99461</v>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>12号屋</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>4030</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2014-08-15</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>412638000</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>102392</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>412638000</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>102392</v>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>15号屋</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>3885</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>115830</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>115830</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1451,7 +1148,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1518,7 +1215,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>12 套</t>
+          <t>10 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1533,7 +1230,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>11 套</t>
+          <t>9 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1594,7 +1291,7 @@
         <is>
           <t>1号屋
 4858呎 (4+房)
-(18年-12月-24日)
+(18年-12月-23日)
 $6.67亿
 $137,201/呎</t>
         </is>
@@ -1603,7 +1300,7 @@
         <is>
           <t>2号屋
 4479呎 (4+房)
-(18年-08月-06日)
+(18年-08月-05日)
 $4.95亿
 $110,538/呎</t>
         </is>
@@ -1621,27 +1318,27 @@
         <is>
           <t>5号屋
 4471呎 (4+房)
-(25年-10月-24日)
+(25年-10月-23日)
 $3.52亿
 $78,730/呎</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>6号屋
-4391呎 (4+房)
-(15年-02月-27日)
-$5.06亿
-$115,247/呎</t>
+          <t>8号屋
+5221呎 (4+房)
+(18年-08月-06日)
+$7.30亿
+$139,820/呎</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>7号屋
-4470呎 (4+房)
-(15年-02月-09日)
-$4.92亿
-$109,998/呎</t>
+          <t>9号屋
+3905呎 (4+房)
+(18年-12月-27日)
+$4.58亿
+$117,286/呎</t>
         </is>
       </c>
     </row>
@@ -1653,58 +1350,42 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>8号屋
-5221呎 (4+房)
-(18年-08月-07日)
-$7.30亿
-$139,820/呎</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>9号屋
-3905呎 (4+房)
-(18年-12月-28日)
-$4.58亿
-$117,286/呎</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
           <t>10号屋
 3845呎 (3房)
-(18年-12月-24日)
+(18年-12月-23日)
 $4.58亿
 $119,116/呎</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>11号屋
 3942呎 (4+房)
-(15年-02月-13日)
+(15年-02月-12日)
 $3.92亿
 $99,461/呎</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>12号屋
 4030呎 (3房)
-(14年-08月-15日)
+(14年-08月-14日)
 $4.13亿
 $102,392/呎</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>15号屋
 3885呎 (4+房)
-(18年-11月-09日)
+(18年-11月-08日)
 $4.50亿
 $115,830/呎</t>
         </is>
       </c>
+      <c r="F7" s="18" t="inlineStr"/>
+      <c r="G7" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
+++ b/港岛-山顶区-Twelve Peaks/Twelve Peaks_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -154,12 +154,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -238,9 +232,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -873,7 +864,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>8号屋</t>
+          <t>6号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -892,7 +883,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5221</v>
+        <v>4391</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -901,14 +892,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2015-02-26</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>730000000</v>
+        <v>506049000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>139820</v>
+        <v>115247</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -919,7 +910,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>7号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -938,7 +929,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3905</v>
+        <v>4470</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -947,14 +938,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2018-12-27</t>
+          <t>2015-02-08</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>458000000</v>
+        <v>491693000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>117286</v>
+        <v>109998</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -965,7 +956,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>8号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -980,11 +971,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3845</v>
+        <v>5221</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -993,14 +984,14 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-12-23</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>458000000</v>
+        <v>730000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>119116</v>
+        <v>139820</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1011,7 +1002,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1030,7 +1021,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3942</v>
+        <v>3905</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1039,14 +1030,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
+          <t>2018-12-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>392074000</v>
+        <v>458000000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>99461</v>
+        <v>117286</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1057,7 +1048,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1076,7 +1067,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4030</v>
+        <v>3845</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1085,14 +1076,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2014-08-14</t>
+          <t>2018-12-23</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>412638000</v>
+        <v>458000000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>102392</v>
+        <v>119116</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1103,44 +1094,136 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>11号屋</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>3942</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>392074000</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>99461</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>12号屋</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>4030</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2014-08-14</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>412638000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>102392</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>15号屋</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>3885</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>2018-11-08</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>450000000</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>115830</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1215,7 +1298,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>10 套</t>
+          <t>12 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1230,7 +1313,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>9 套</t>
+          <t>11 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1325,6 +1408,31 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
+          <t>6号屋
+4391呎 (4+房)
+(15年-02月-26日)
+$5.06亿
+$115,247/呎</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>7号屋
+4470呎 (4+房)
+(15年-02月-08日)
+$4.92亿
+$109,998/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
           <t>8号屋
 5221呎 (4+房)
 (18年-08月-06日)
@@ -1332,7 +1440,7 @@
 $139,820/呎</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>9号屋
 3905呎 (4+房)
@@ -1341,14 +1449,7 @@
 $117,286/呎</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>第 2 行</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>10号屋
 3845呎 (3房)
@@ -1357,7 +1458,7 @@
 $119,116/呎</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>11号屋
 3942呎 (4+房)
@@ -1366,7 +1467,7 @@
 $99,461/呎</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>12号屋
 4030呎 (3房)
@@ -1375,7 +1476,7 @@
 $102,392/呎</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>15号屋
 3885呎 (4+房)
@@ -1384,8 +1485,6 @@
 $115,830/呎</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr"/>
-      <c r="G7" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
